--- a/data/trans_orig/IP07_C16_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C16_2023-Habitat-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han sufrido cyberbulling en 2023 (tasa de respuesta: 99,48%)</t>
+          <t>Menores según si han sufrido cyberbulling en su colegio/instituto o fuera de él en 2023 (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>45301</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>40951</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>47016</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>95,31%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>86,16%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>98,92%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>30717</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>28651</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>98,54%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>91,91%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>33690</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>31937</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>34180</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>98,57%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>93,44%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>45630</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>41340</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>48021</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>95,02%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>86,09%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>99</t>
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>76348</t>
+          <t>78991</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71582</t>
+          <t>74737</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78459</t>
+          <t>80928</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2227</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6577</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>13,84%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2522</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2243</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,09%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2391</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6681</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2846</t>
+          <t>2717</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>780</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7612</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>93808</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>78476</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>99012</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,04%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>76,99%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,14%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>49973</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>45381</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>51863</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>93,86%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>85,23%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,41%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>93522</t>
+          <t>53592</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76157</t>
+          <t>49155</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99571</t>
+          <t>55750</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>143496</t>
+          <t>147400</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>126179</t>
+          <t>132821</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>150030</t>
+          <t>153087</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>19924</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>827</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22577</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26851</t>
+          <t>22585</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3807</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1501</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8230</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2517</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6474</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,16%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9399</t>
+          <t>6211</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11453</t>
+          <t>11551</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>53242</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>53242</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>53242</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>56885</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>56885</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>56885</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>156019</t>
+          <t>158809</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>156019</t>
+          <t>158809</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>156019</t>
+          <t>158809</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,72 +1632,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>61117</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56655</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>63952</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>95,57%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>88,59%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>41391</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>16026</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>67808</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>57,34%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>22,2%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>93,94%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>61365</t>
+          <t>42452</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56796</t>
+          <t>32991</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63345</t>
+          <t>46510</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>102755</t>
+          <t>103569</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>58131</t>
+          <t>93072</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>129944</t>
+          <t>108384</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -1745,72 +1745,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>28620</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1838</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>55599</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>39,65%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>77,03%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>853</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14245</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>28620</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76922</t>
+          <t>16514</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5985</t>
+          <t>7297</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2792</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>751</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7361</t>
+          <t>5835</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1576</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10932</t>
+          <t>11491</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>63952</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>63952</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>63952</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64157</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64157</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>64157</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>136340</t>
+          <t>113270</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>136340</t>
+          <t>113270</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>136340</t>
+          <t>113270</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,72 +2088,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>54870</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>50843</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>98,3%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>91,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>50637</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>46812</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>52127</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>95,95%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>88,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>55435</t>
+          <t>53929</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51821</t>
+          <t>49931</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>55420</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>106073</t>
+          <t>108797</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101579</t>
+          <t>104378</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>108295</t>
+          <t>111037</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -2201,107 +2201,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4977</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>8,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>936</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>4550</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>5612</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>936</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>5326</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -2314,72 +2314,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2137</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>5962</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,3%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>633</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>52774</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>52774</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>52774</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56059</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56059</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56059</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>109145</t>
+          <t>111878</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>109145</t>
+          <t>111878</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>109145</t>
+          <t>111878</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2544,72 +2544,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>255095</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>240135</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>261993</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>94,75%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>89,2%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>97,31%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>172717</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>111625</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>199742</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>82,49%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>53,31%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>95,4%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>255953</t>
+          <t>183661</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>234539</t>
+          <t>172982</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>262989</t>
+          <t>189085</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>428671</t>
+          <t>438757</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>340510</t>
+          <t>421382</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>459204</t>
+          <t>448408</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -2657,72 +2657,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>24872</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>9,24%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>29372</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>1788</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>91786</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>43,84%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28623</t>
+          <t>15946</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>35511</t>
+          <t>10550</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>128736</t>
+          <t>27679</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -2770,72 +2770,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4558</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>15630</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5,81%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>7281</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>3326</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>13710</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>6,55%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16410</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>16516</t>
+          <t>16358</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>9855</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24064</t>
+          <t>24428</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>269223</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>269223</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>269223</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>209371</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>209371</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>209371</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>271326</t>
+          <t>196441</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>271326</t>
+          <t>196441</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>271326</t>
+          <t>196441</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>480698</t>
+          <t>465665</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>480698</t>
+          <t>465665</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>480698</t>
+          <t>465665</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
